--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$17</definedName>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$17</definedName>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8.0  |  13 controls</t>
+          <t>Role: M365 Global Admin / Copilot Admin  |  FSI Copilot Governance Framework v1.8.0  |  15 controls</t>
         </is>
       </c>
     </row>
@@ -685,17 +685,17 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Copilot Admin Settings and Feature Management</t>
+          <t>Cross-Tenant Agent Federation (MCP and Entra Agent ID)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>P4 – Operations &amp; Lifecycle</t>
+          <t>P2 – Security &amp; Data Protection</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+          <t>Copilot Chat; Pages; Agents; Purview DLP/Labels</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Are Microsoft 365 Copilot admin settings reviewed and configured per the organization's governance policy on a documented cadence?</t>
+          <t>Are cross-tenant Entra Agent ID trust relationships, MCP federated server attestations, and Copilot Studio multi-tenant publishings subject to documented approval and review?</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>List of users assigned 'AI Administrator' role with last sign-in; Cloud Policy export covering Copilot Pages / Notebooks / code preview decisions; Pay-as-you-go (PAYG) services configuration screenshot + budget alert thresholds; Change-management record (ticket / PR) for the most recent Copilot setting toggle; Documented review cadence (monthly / quarterly) with evidence-pack template</t>
+          <t>Cross-tenant trust relationship inventory with named owners; Approval records for each trust relationship; MCP federated server attestation documentation; Periodic review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -724,12 +724,12 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Copilot in Teams Meetings Governance</t>
+          <t>Copilot Admin Settings and Feature Management</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Are Teams meeting policies governing Copilot in meetings, including transcription prerequisites, reviewed on a documented cadence?</t>
+          <t>Are Microsoft 365 Copilot admin settings reviewed and configured per the organization's governance policy on a documented cadence?</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Teams meeting policy configuration showing Copilot settings; Meeting organizer control documentation; Transcription retention policy aligned to regulatory requirements; Governance policy document for Copilot in meetings</t>
+          <t>List of users assigned 'AI Administrator' role with last sign-in; Cloud Policy export covering Copilot Pages / Notebooks / code preview decisions; Pay-as-you-go (PAYG) services configuration screenshot + budget alert thresholds; Change-management record (ticket / PR) for the most recent Copilot setting toggle; Documented review cadence (monthly / quarterly) with evidence-pack template</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -763,12 +763,12 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Copilot in Teams Phone and Queues Governance</t>
+          <t>Copilot in Teams Meetings Governance</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Are Teams calling and voice-application policies that expose Copilot features reviewed on a documented cadence?</t>
+          <t>Are Teams meeting policies governing Copilot in meetings, including transcription prerequisites, reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Teams calling policy configuration for Copilot features; Call-recording retention policy aligned to regulatory minimum; Governance document covering call summarization and analytics; Queue configuration with Copilot feature settings</t>
+          <t>Teams meeting policy configuration showing Copilot settings; Meeting organizer control documentation; Transcription retention policy aligned to regulatory requirements; Governance policy document for Copilot in meetings</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -802,12 +802,12 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Copilot in Viva Suite Governance</t>
+          <t>Copilot in Teams Phone and Queues Governance</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Is Viva-suite Copilot integration (Insights, Engage, Topics) reviewed on a documented governance cadence?</t>
+          <t>Are Teams calling and voice-application policies that expose Copilot features reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Viva Copilot governance policy document; Privacy control configuration for Viva Insights; Approved user group scoping for Copilot features; Governance review cadence and most recent review date</t>
+          <t>Teams calling policy configuration for Copilot features; Call-recording retention policy aligned to regulatory minimum; Governance document covering call summarization and analytics; Queue configuration with Copilot feature settings</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -841,12 +841,12 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Copilot Usage Analytics and Adoption Reporting</t>
+          <t>Copilot in Viva Suite Governance</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Are Copilot usage analytics reported to leadership on a documented cadence with anomalies flagged?</t>
+          <t>Is Viva-suite Copilot integration (Insights, Engage, Topics) reviewed on a documented governance cadence?</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Successful Microsoft Graph beta usage-detail export artifact (JSON or CSV) with timestamp and period; At least one usage-detail record returned for the selected period (fail closed if empty); Permission evidence for Reports.Read.All and supported delegated role or app consent; Documented caveats for beta API behavior, national-cloud availability (global only), and unlicensed Copilot Chat data exclusion</t>
+          <t>Viva Copilot governance policy document; Privacy control configuration for Viva Insights; Approved user group scoping for Copilot features; Governance review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -880,12 +880,12 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Copilot Feedback and Telemetry Data Governance</t>
+          <t>Copilot Usage Analytics and Adoption Reporting</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Is Copilot feedback / thumb-rating telemetry reviewed on a documented cadence and routed to product owners?</t>
+          <t>Are Copilot usage analytics reported to leadership on a documented cadence with anomalies flagged?</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Feedback review cadence and routing documentation; Privacy controls for feedback/telemetry data handling; Product owner assignment for feedback triage; Most recent feedback review summary</t>
+          <t>Successful Microsoft Graph beta usage-detail export artifact (JSON or CSV) with timestamp and period; At least one usage-detail record returned for the selected period (fail closed if empty); Permission evidence for Reports.Read.All and supported delegated role or app consent; Documented caveats for beta API behavior, national-cloud availability (global only), and unlicensed Copilot Chat data exclusion</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -919,12 +919,12 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cost Allocation and License Optimization</t>
+          <t>Copilot Feedback and Telemetry Data Governance</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Is Copilot license cost allocation reviewed and chargeback / showback executed on a documented cadence?</t>
+          <t>Is Copilot feedback / thumb-rating telemetry reviewed on a documented cadence and routed to product owners?</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Cost allocation report by business unit / cost center; License reclamation cadence and recent reclamation records; PAYG cost tracking dashboard with budget alerts; Chargeback/showback documentation</t>
+          <t>Feedback review cadence and routing documentation; Privacy controls for feedback/telemetry data handling; Product owner assignment for feedback triage; Most recent feedback review summary</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -958,12 +958,12 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Change Management for Copilot Feature Rollouts</t>
+          <t>Cost Allocation and License Optimization</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Are Copilot feature releases (Microsoft-managed and tenant-managed) tracked and risk-reviewed before user enablement?</t>
+          <t>Is Copilot license cost allocation reviewed and chargeback / showback executed on a documented cadence?</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Change advisory board records for Copilot feature rollouts; M365 Message Center monitoring evidence; Risk review documentation for recent feature changes; Approval records for tenant-managed feature enablement</t>
+          <t>Cost allocation report by business unit / cost center; License reclamation cadence and recent reclamation records; PAYG cost tracking dashboard with budget alerts; Chargeback/showback documentation</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr"/>
@@ -997,12 +997,12 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Copilot Cowork Governance</t>
+          <t>Change Management for Copilot Feature Rollouts</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Is Microsoft 365 Copilot Cowork governed at GA with deliberate billing/discovery, model/browser, plugin/skill, and supervision decisions before broad enablement?</t>
+          <t>Are Copilot feature releases (Microsoft-managed and tenant-managed) tracked and risk-reviewed before user enablement?</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+          <t>Change advisory board records for Copilot feature rollouts; M365 Message Center monitoring evidence; Risk review documentation for recent feature changes; Approval records for tenant-managed feature enablement</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Microsoft Scout Governance</t>
+          <t>Copilot Studio Agent Lifecycle Governance</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1061,25 +1061,103 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+          <t>Is the Copilot Studio agent lifecycle (authoring → testing → publishing → versioning → deprecation) governed with documented evidence at each gate?</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Agent lifecycle governance policy document; Lifecycle gate evidence (testing, approval, publishing records); Agent inventory with lifecycle stage tracking; Retirement/deprecation documentation for decommissioned agents</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Copilot Cowork Governance</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft 365 Copilot Cowork governed at GA with deliberate billing/discovery, model/browser, plugin/skill, and supervision decisions before broad enablement?</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I17"/>
+  <autoFilter ref="A4:I19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$19</definedName>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M365 Global Admin - Copilot Adm" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M365 Global Admin - Copilot Adm'!$A$4:$I$19</definedName>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Current discovery-setting decision record, transition note, and access-request workflow evidence; Model-policy record for Anthropic family and any enabled provider-retention model variants; Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy plus recent Cost management and Cowork usage reports; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
+++ b/docs/assessment/templates/m365-global-admin-or-copilot-admin-checklist.xlsx
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved tool-server inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local tool output, third-party inference telemetry)</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
